--- a/EKG_Kalite_Yönetim_Sistemi/15_Katmanlı Denetim ve Yetkinlik/03_Öznel Kontrol Yapan Personelin Değerlendirilmesi/EKG-IK-FRM-01_operator_karar_uyum_ve_yeniden_yetkilendirme_kaydi.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/15_Katmanlı Denetim ve Yetkinlik/03_Öznel Kontrol Yapan Personelin Değerlendirilmesi/EKG-IK-FRM-01_operator_karar_uyum_ve_yeniden_yetkilendirme_kaydi.xlsx
@@ -850,7 +850,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-IK-FRM-01&amp;C&amp;"Arial,Regular"&amp;11Operatör Karar Uyum ve Yeniden Yetkilendirme Kaydı</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 12.06.2026 | Revizyon: 25.09.2026
+Revizyon nedeni: Kappa iddiası kaldırıldı; tamamlanmış kör deneme çiftleri, ham uyum, referans doğruluğu ve ayrı yetki onayı kuruldu.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -1215,7 +1216,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-IK-FRM-01&amp;C&amp;"Arial,Regular"&amp;11Operatör Karar Uyum ve Yeniden Yetkilendirme Kaydı</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 12.06.2026 | Revizyon: 25.09.2026
+Revizyon nedeni: Kappa iddiası kaldırıldı; tamamlanmış kör deneme çiftleri, ham uyum, referans doğruluğu ve ayrı yetki onayı kuruldu.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>